--- a/Donnees/Statistiques Démographiques et sociales/Education/Theme_Education.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Education/Theme_Education.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Education\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB6686F-CC32-4C3A-8BD5-D4A864A1FD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEC147F-14D6-42BC-BF48-96D383ED7DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garçons" sheetId="1" r:id="rId1"/>
@@ -211,16 +211,19 @@
       <b/>
       <sz val="13"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
